--- a/src/main/resources/menuItems/Sales/Transactions/480464 - Sales Return with Invoice Reference-AC.xlsx
+++ b/src/main/resources/menuItems/Sales/Transactions/480464 - Sales Return with Invoice Reference-AC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\IdeaProjects\wings-testautomation\src\main\resources\menuItems\Sales\Transactions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\IdeaProjects\Wings-Automation\src\main\resources\menuItems\Sales\Transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03D237D6-D215-4327-9226-4F46A08763AF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3825DB9A-5FF2-431D-ABDB-ADE13D4B3632}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32760" yWindow="32760" windowWidth="32760" windowHeight="32760" tabRatio="938" activeTab="2"/>
+    <workbookView xWindow="32760" yWindow="32760" windowWidth="32760" windowHeight="32760" tabRatio="938" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tables" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="616">
   <si>
     <t>TableNames</t>
   </si>
@@ -1887,12 +1887,15 @@
   </si>
   <si>
     <t>Cost Of Goods Sold per Unit</t>
+  </si>
+  <si>
+    <t>ī</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1901,7 +1904,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1920,6 +1923,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1933,12 +1942,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2246,7 +2259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -2516,7 +2529,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -2578,7 +2591,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -2636,7 +2649,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -2835,7 +2848,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -3205,7 +3218,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -3479,7 +3492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -3735,7 +3748,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -3769,7 +3782,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -3803,7 +3816,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -3868,7 +3881,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -3988,7 +4001,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -4162,7 +4175,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -4607,7 +4620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -4711,7 +4724,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -4815,7 +4828,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -4900,11 +4913,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:BX18"/>
+  <dimension ref="A1:BX28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -5905,23 +5918,23 @@
       <c r="D5" t="s">
         <v>191</v>
       </c>
-      <c r="E5" t="s">
-        <v>138</v>
+      <c r="E5">
+        <v>8967</v>
       </c>
       <c r="F5" t="s">
         <v>139</v>
       </c>
-      <c r="G5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H5" t="s">
-        <v>53</v>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
       </c>
       <c r="I5" t="s">
         <v>193</v>
       </c>
       <c r="J5" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="K5" t="s">
         <v>195</v>
@@ -5939,58 +5952,58 @@
         <v>143</v>
       </c>
       <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
         <v>1</v>
       </c>
-      <c r="Q5">
+      <c r="U5">
         <v>1</v>
       </c>
-      <c r="R5">
+      <c r="V5">
         <v>1</v>
       </c>
-      <c r="S5">
+      <c r="W5">
         <v>1</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
       </c>
       <c r="X5">
         <v>500.14</v>
       </c>
       <c r="Y5">
-        <v>500.14</v>
+        <v>0</v>
       </c>
       <c r="Z5">
         <v>250.14</v>
       </c>
       <c r="AA5">
-        <v>250.14</v>
-      </c>
-      <c r="AB5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="5">
         <v>0</v>
       </c>
       <c r="AD5">
         <v>1.1100000000000001</v>
       </c>
       <c r="AE5">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="AG5">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="s">
         <v>196</v>
@@ -5999,7 +6012,7 @@
         <v>1.05</v>
       </c>
       <c r="AJ5">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="s">
         <v>196</v>
@@ -6008,7 +6021,7 @@
         <v>1.21</v>
       </c>
       <c r="AM5">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="s">
         <v>197</v>
@@ -6017,10 +6030,10 @@
         <v>1.26</v>
       </c>
       <c r="AP5">
-        <v>3.12</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
       </c>
       <c r="AR5" t="s">
         <v>145</v>
@@ -6032,31 +6045,31 @@
         <v>147</v>
       </c>
       <c r="AU5">
-        <v>239.1</v>
+        <v>0</v>
       </c>
       <c r="AV5">
         <v>12</v>
       </c>
       <c r="AW5">
-        <v>14.35</v>
+        <v>0</v>
       </c>
       <c r="AX5">
-        <v>14.35</v>
+        <v>0</v>
       </c>
       <c r="AY5">
         <v>0</v>
       </c>
       <c r="AZ5">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BA5">
-        <v>31.09</v>
+        <v>0</v>
       </c>
       <c r="BB5">
-        <v>270.19</v>
+        <v>0</v>
       </c>
       <c r="BC5">
-        <v>270.19</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="s">
         <v>198</v>
@@ -6071,55 +6084,55 @@
         <v>201</v>
       </c>
       <c r="BH5" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="BI5" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="BJ5" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="BK5" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="BL5" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="BM5" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="BN5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BO5">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="BP5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BQ5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BR5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BS5" s="1">
-        <v>45859</v>
+        <v>45862</v>
       </c>
       <c r="BT5" s="1">
-        <v>45860</v>
+        <v>45863</v>
       </c>
       <c r="BU5" s="1">
-        <v>45861</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>53</v>
-      </c>
-      <c r="BW5" t="s">
-        <v>53</v>
-      </c>
-      <c r="BX5" t="s">
-        <v>53</v>
+        <v>45864</v>
+      </c>
+      <c r="BV5" s="6">
+        <v>1</v>
+      </c>
+      <c r="BW5" s="6">
+        <v>1</v>
+      </c>
+      <c r="BX5" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:76" x14ac:dyDescent="0.25">
@@ -6135,23 +6148,23 @@
       <c r="D6" t="s">
         <v>191</v>
       </c>
-      <c r="E6" t="s">
-        <v>138</v>
+      <c r="E6">
+        <v>8967</v>
       </c>
       <c r="F6" t="s">
         <v>139</v>
       </c>
-      <c r="G6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" t="s">
-        <v>53</v>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
       </c>
       <c r="I6" t="s">
         <v>193</v>
       </c>
       <c r="J6" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="K6" t="s">
         <v>195</v>
@@ -6169,58 +6182,58 @@
         <v>143</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6">
         <v>500.14</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>500.14</v>
       </c>
       <c r="Z6">
         <v>250.14</v>
       </c>
       <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="4">
+        <v>250.14</v>
+      </c>
+      <c r="AB6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="5">
         <v>0</v>
       </c>
       <c r="AD6">
         <v>1.1100000000000001</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF6">
-        <v>1.1599999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH6" t="s">
         <v>196</v>
@@ -6229,7 +6242,7 @@
         <v>1.05</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK6" t="s">
         <v>196</v>
@@ -6238,7 +6251,7 @@
         <v>1.21</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN6" t="s">
         <v>197</v>
@@ -6247,10 +6260,10 @@
         <v>1.26</v>
       </c>
       <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>57</v>
+        <v>3.12</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
       </c>
       <c r="AR6" t="s">
         <v>145</v>
@@ -6262,31 +6275,31 @@
         <v>147</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>239.1</v>
       </c>
       <c r="AV6">
         <v>12</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>14.35</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>14.35</v>
       </c>
       <c r="AY6">
         <v>0</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>31.09</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>270.19</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>270.19</v>
       </c>
       <c r="BD6" t="s">
         <v>198</v>
@@ -6301,55 +6314,55 @@
         <v>201</v>
       </c>
       <c r="BH6" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="BI6" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="BJ6" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="BK6" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="BL6" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="BM6" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="BN6">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO6">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BP6">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BQ6">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BR6">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BS6" s="1">
-        <v>45862</v>
+        <v>45859</v>
       </c>
       <c r="BT6" s="1">
-        <v>45863</v>
+        <v>45860</v>
       </c>
       <c r="BU6" s="1">
-        <v>45864</v>
-      </c>
-      <c r="BV6" t="s">
-        <v>53</v>
-      </c>
-      <c r="BW6" t="s">
-        <v>53</v>
-      </c>
-      <c r="BX6" t="s">
-        <v>53</v>
+        <v>45861</v>
+      </c>
+      <c r="BV6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BW6" s="6">
+        <v>1</v>
+      </c>
+      <c r="BX6" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:76" x14ac:dyDescent="0.25">
@@ -6712,85 +6725,85 @@
     <row r="13" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AA13" s="3">
         <f t="shared" si="0"/>
-        <v>250.14</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="3">
         <f t="shared" si="5"/>
-        <v>2.776554</v>
+        <v>0</v>
       </c>
       <c r="AG13" s="3">
         <f t="shared" si="5"/>
-        <v>2.8766099999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ13" s="3">
         <f>$R5*AI5</f>
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AM13" s="3">
         <f>$R5*AL5</f>
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP13" s="3">
         <f>($AA13-AJ13-AM13)*AO5%</f>
-        <v>3.1232879999999996</v>
+        <v>0</v>
       </c>
       <c r="AS13" s="3">
         <f t="shared" si="1"/>
-        <v>11.036452000000001</v>
+        <v>0</v>
       </c>
       <c r="AU13" s="3">
         <f t="shared" si="2"/>
-        <v>239.10354799999999</v>
+        <v>0</v>
       </c>
       <c r="BA13" s="3">
         <f t="shared" si="3"/>
-        <v>31.08242576</v>
+        <v>0</v>
       </c>
       <c r="BB13" s="3">
         <f t="shared" si="4"/>
-        <v>270.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AA14" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>250.14</v>
       </c>
       <c r="AE14" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.776554</v>
       </c>
       <c r="AG14" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8766099999999999</v>
       </c>
       <c r="AJ14" s="3">
         <f>$R6*AI6</f>
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AM14" s="3">
         <f>$R6*AL6</f>
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP14" s="3">
         <f>($AA14-AJ14-AM14)*AO6%</f>
-        <v>0</v>
+        <v>3.1232879999999996</v>
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11.036452000000001</v>
       </c>
       <c r="AU14" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>239.10354799999999</v>
       </c>
       <c r="BA14" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>31.08242576</v>
       </c>
       <c r="BB14" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>270.19</v>
       </c>
     </row>
     <row r="15" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6836,7 +6849,7 @@
       </c>
     </row>
     <row r="16" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="27:54" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="27:72" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AA17" s="3">
         <f>SUM(AA10:AA15)</f>
         <v>1205.0627899999999</v>
@@ -6878,7 +6891,7 @@
         <v>1349.27</v>
       </c>
     </row>
-    <row r="18" spans="27:54" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="27:72" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="AA18" s="3">
         <f>SUM(AA2:AA7)</f>
         <v>1205.06</v>
@@ -6934,6 +6947,11 @@
       <c r="BB18" s="3">
         <f t="shared" si="6"/>
         <v>1349.18</v>
+      </c>
+    </row>
+    <row r="28" spans="27:72" x14ac:dyDescent="0.25">
+      <c r="BT28" t="s">
+        <v>615</v>
       </c>
     </row>
   </sheetData>
@@ -6943,7 +6961,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -7400,7 +7418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -7920,7 +7938,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -8740,7 +8758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -9560,7 +9578,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
@@ -9670,7 +9688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>

--- a/src/main/resources/menuItems/Sales/Transactions/480464 - Sales Return with Invoice Reference-AC.xlsx
+++ b/src/main/resources/menuItems/Sales/Transactions/480464 - Sales Return with Invoice Reference-AC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\IdeaProjects\Wings-Automation\src\main\resources\menuItems\Sales\Transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3825DB9A-5FF2-431D-ABDB-ADE13D4B3632}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71E4B4F-0FF3-4C27-8033-DF2AE95BD35A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32760" yWindow="32760" windowWidth="32760" windowHeight="32760" tabRatio="938" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5918,7 +5918,7 @@
       <c r="D5" t="s">
         <v>191</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="6">
         <v>8967</v>
       </c>
       <c r="F5" t="s">
@@ -6148,7 +6148,7 @@
       <c r="D6" t="s">
         <v>191</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="6">
         <v>8967</v>
       </c>
       <c r="F6" t="s">

--- a/src/main/resources/menuItems/Sales/Transactions/480464 - Sales Return with Invoice Reference-AC.xlsx
+++ b/src/main/resources/menuItems/Sales/Transactions/480464 - Sales Return with Invoice Reference-AC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\IdeaProjects\Wings-Automation\src\main\resources\menuItems\Sales\Transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B71E4B4F-0FF3-4C27-8033-DF2AE95BD35A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77185577-FD6D-4B2D-A660-5EAA1B260204}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32760" yWindow="32760" windowWidth="32760" windowHeight="32760" tabRatio="938" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="619">
   <si>
     <t>TableNames</t>
   </si>
@@ -260,9 +260,6 @@
     <t>Product</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
     <t>HSNCode</t>
   </si>
   <si>
@@ -1890,6 +1887,18 @@
   </si>
   <si>
     <t>ī</t>
+  </si>
+  <si>
+    <t>MasterType</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>Products - Batches and Serial No</t>
+  </si>
+  <si>
+    <t>Products - MultiBatch</t>
   </si>
 </sst>
 </file>
@@ -1904,7 +1913,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1929,6 +1938,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1942,7 +1957,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1952,6 +1967,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2546,22 +2562,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1" t="s">
         <v>345</v>
       </c>
-      <c r="B1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>346</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>347</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>348</v>
-      </c>
-      <c r="F1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2581,7 +2597,7 @@
         <v>67.89</v>
       </c>
       <c r="F2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -2612,34 +2628,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B1" t="s">
         <v>69</v>
       </c>
       <c r="C1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D1" t="s">
         <v>352</v>
-      </c>
-      <c r="D1" t="s">
-        <v>353</v>
       </c>
       <c r="E1" t="s">
         <v>46</v>
       </c>
       <c r="F1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G1" t="s">
         <v>354</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>355</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>356</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>357</v>
-      </c>
-      <c r="J1" t="s">
-        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -2669,39 +2685,39 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B1" t="s">
         <v>359</v>
       </c>
-      <c r="B1" t="s">
-        <v>360</v>
-      </c>
       <c r="C1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" t="s">
         <v>115</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>116</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>117</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>118</v>
-      </c>
-      <c r="I1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C2">
         <v>11.11</v>
@@ -2710,27 +2726,27 @@
         <v>11.11</v>
       </c>
       <c r="E2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F2" t="s">
         <v>362</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>363</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>364</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>365</v>
-      </c>
-      <c r="I2" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C3">
         <v>11.12</v>
@@ -2739,27 +2755,27 @@
         <v>11.12</v>
       </c>
       <c r="E3" t="s">
+        <v>367</v>
+      </c>
+      <c r="F3" t="s">
         <v>368</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>369</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>370</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>371</v>
-      </c>
-      <c r="I3" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C4">
         <v>11.13</v>
@@ -2768,27 +2784,27 @@
         <v>11.13</v>
       </c>
       <c r="E4" t="s">
+        <v>373</v>
+      </c>
+      <c r="F4" t="s">
         <v>374</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>375</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>376</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>377</v>
-      </c>
-      <c r="I4" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C5">
         <v>11.14</v>
@@ -2797,27 +2813,27 @@
         <v>11.14</v>
       </c>
       <c r="E5" t="s">
+        <v>379</v>
+      </c>
+      <c r="F5" t="s">
         <v>380</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>381</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>382</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>383</v>
-      </c>
-      <c r="I5" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C6">
         <v>11.15</v>
@@ -2826,19 +2842,19 @@
         <v>11.15</v>
       </c>
       <c r="E6" t="s">
+        <v>385</v>
+      </c>
+      <c r="F6" t="s">
         <v>386</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>387</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>388</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>389</v>
-      </c>
-      <c r="I6" t="s">
-        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -2877,66 +2893,66 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1" t="s">
         <v>391</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E1" t="s">
         <v>392</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
+        <v>393</v>
+      </c>
+      <c r="G1" t="s">
+        <v>394</v>
+      </c>
+      <c r="H1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I1" t="s">
+        <v>396</v>
+      </c>
+      <c r="J1" t="s">
         <v>237</v>
       </c>
-      <c r="D1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E1" t="s">
-        <v>393</v>
-      </c>
-      <c r="F1" t="s">
-        <v>394</v>
-      </c>
-      <c r="G1" t="s">
-        <v>395</v>
-      </c>
-      <c r="H1" t="s">
-        <v>396</v>
-      </c>
-      <c r="I1" t="s">
-        <v>397</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>238</v>
       </c>
-      <c r="K1" t="s">
-        <v>239</v>
-      </c>
       <c r="L1" t="s">
+        <v>112</v>
+      </c>
+      <c r="M1" t="s">
         <v>113</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>114</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>115</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>116</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>117</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>118</v>
-      </c>
-      <c r="R1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C2">
         <v>12.11</v>
@@ -2945,19 +2961,19 @@
         <v>13.32</v>
       </c>
       <c r="E2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F2" s="1">
         <v>45880</v>
       </c>
       <c r="G2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J2">
         <v>1.21</v>
@@ -2972,27 +2988,27 @@
         <v>13.32</v>
       </c>
       <c r="N2" t="s">
+        <v>400</v>
+      </c>
+      <c r="O2" t="s">
         <v>401</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>402</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>403</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>404</v>
-      </c>
-      <c r="R2" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C3">
         <v>12.12</v>
@@ -3001,19 +3017,19 @@
         <v>13.34</v>
       </c>
       <c r="E3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F3" s="1">
         <v>45881</v>
       </c>
       <c r="G3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J3">
         <v>1.22</v>
@@ -3028,27 +3044,27 @@
         <v>13.34</v>
       </c>
       <c r="N3" t="s">
+        <v>408</v>
+      </c>
+      <c r="O3" t="s">
         <v>409</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>410</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>411</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>412</v>
-      </c>
-      <c r="R3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C4">
         <v>12.13</v>
@@ -3057,19 +3073,19 @@
         <v>13.36</v>
       </c>
       <c r="E4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F4" s="1">
         <v>45882</v>
       </c>
       <c r="G4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J4">
         <v>1.23</v>
@@ -3084,27 +3100,27 @@
         <v>13.36</v>
       </c>
       <c r="N4" t="s">
+        <v>416</v>
+      </c>
+      <c r="O4" t="s">
         <v>417</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>418</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>419</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>420</v>
-      </c>
-      <c r="R4" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C5">
         <v>12.14</v>
@@ -3113,19 +3129,19 @@
         <v>13.38</v>
       </c>
       <c r="E5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F5" s="1">
         <v>45883</v>
       </c>
       <c r="G5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I5" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J5">
         <v>1.24</v>
@@ -3140,27 +3156,27 @@
         <v>13.38</v>
       </c>
       <c r="N5" t="s">
+        <v>424</v>
+      </c>
+      <c r="O5" t="s">
         <v>425</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>426</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>427</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>428</v>
-      </c>
-      <c r="R5" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C6">
         <v>12.15</v>
@@ -3169,19 +3185,19 @@
         <v>13.4</v>
       </c>
       <c r="E6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F6" s="1">
         <v>45884</v>
       </c>
       <c r="G6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="I6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="J6">
         <v>1.25</v>
@@ -3196,19 +3212,19 @@
         <v>13.4</v>
       </c>
       <c r="N6" t="s">
+        <v>432</v>
+      </c>
+      <c r="O6" t="s">
         <v>433</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>434</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>435</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>436</v>
-      </c>
-      <c r="R6" t="s">
-        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -3241,54 +3257,54 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1" t="s">
         <v>391</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D1" t="s">
+        <v>236</v>
+      </c>
+      <c r="E1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F1" t="s">
         <v>392</v>
       </c>
-      <c r="C1" t="s">
-        <v>438</v>
-      </c>
-      <c r="D1" t="s">
-        <v>237</v>
-      </c>
-      <c r="E1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>393</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>394</v>
       </c>
-      <c r="H1" t="s">
-        <v>395</v>
-      </c>
       <c r="I1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" t="s">
         <v>115</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>116</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>117</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>118</v>
-      </c>
-      <c r="M1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C2" t="s">
         <v>439</v>
-      </c>
-      <c r="B2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C2" t="s">
-        <v>440</v>
       </c>
       <c r="D2">
         <v>13.11</v>
@@ -3297,39 +3313,39 @@
         <v>13.11</v>
       </c>
       <c r="F2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G2" s="1">
         <v>45885</v>
       </c>
       <c r="H2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="I2" t="s">
+        <v>441</v>
+      </c>
+      <c r="J2" t="s">
         <v>442</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>443</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>444</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>445</v>
-      </c>
-      <c r="M2" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D3">
         <v>13.12</v>
@@ -3338,39 +3354,39 @@
         <v>13.12</v>
       </c>
       <c r="F3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G3" s="1">
         <v>45886</v>
       </c>
       <c r="H3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="I3" t="s">
+        <v>448</v>
+      </c>
+      <c r="J3" t="s">
         <v>449</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>450</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>451</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>452</v>
-      </c>
-      <c r="M3" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D4">
         <v>13.13</v>
@@ -3379,39 +3395,39 @@
         <v>13.13</v>
       </c>
       <c r="F4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G4" s="1">
         <v>45887</v>
       </c>
       <c r="H4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I4" t="s">
+        <v>455</v>
+      </c>
+      <c r="J4" t="s">
         <v>456</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>457</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>458</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>459</v>
-      </c>
-      <c r="M4" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C5" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D5">
         <v>13.14</v>
@@ -3420,39 +3436,39 @@
         <v>13.14</v>
       </c>
       <c r="F5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G5" s="1">
         <v>45888</v>
       </c>
       <c r="H5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I5" t="s">
+        <v>462</v>
+      </c>
+      <c r="J5" t="s">
         <v>463</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>464</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>465</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>466</v>
-      </c>
-      <c r="M5" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D6">
         <v>13.15</v>
@@ -3461,28 +3477,28 @@
         <v>13.15</v>
       </c>
       <c r="F6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G6" s="1">
         <v>45889</v>
       </c>
       <c r="H6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I6" t="s">
+        <v>469</v>
+      </c>
+      <c r="J6" t="s">
         <v>470</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>471</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>472</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>473</v>
-      </c>
-      <c r="M6" t="s">
-        <v>474</v>
       </c>
     </row>
   </sheetData>
@@ -3515,48 +3531,48 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1" t="s">
         <v>391</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E1" t="s">
         <v>392</v>
       </c>
-      <c r="C1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>393</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>394</v>
       </c>
-      <c r="G1" t="s">
-        <v>395</v>
-      </c>
       <c r="H1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I1" t="s">
         <v>115</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>116</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>117</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>118</v>
-      </c>
-      <c r="L1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C2">
         <v>14.11</v>
@@ -3565,36 +3581,36 @@
         <v>14.11</v>
       </c>
       <c r="E2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F2" s="1">
         <v>45890</v>
       </c>
       <c r="G2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2" t="s">
+        <v>476</v>
+      </c>
+      <c r="I2" t="s">
         <v>477</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>478</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>479</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>480</v>
-      </c>
-      <c r="L2" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B3" t="s">
         <v>482</v>
-      </c>
-      <c r="B3" t="s">
-        <v>483</v>
       </c>
       <c r="C3">
         <v>14.12</v>
@@ -3603,36 +3619,36 @@
         <v>14.12</v>
       </c>
       <c r="E3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F3" s="1">
         <v>45891</v>
       </c>
       <c r="G3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H3" t="s">
+        <v>484</v>
+      </c>
+      <c r="I3" t="s">
         <v>485</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>486</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>487</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>488</v>
-      </c>
-      <c r="L3" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>489</v>
+      </c>
+      <c r="B4" t="s">
         <v>490</v>
-      </c>
-      <c r="B4" t="s">
-        <v>491</v>
       </c>
       <c r="C4">
         <v>14.13</v>
@@ -3641,36 +3657,36 @@
         <v>14.13</v>
       </c>
       <c r="E4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F4" s="1">
         <v>45892</v>
       </c>
       <c r="G4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H4" t="s">
+        <v>492</v>
+      </c>
+      <c r="I4" t="s">
         <v>493</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>494</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>495</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>496</v>
-      </c>
-      <c r="L4" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>497</v>
+      </c>
+      <c r="B5" t="s">
         <v>498</v>
-      </c>
-      <c r="B5" t="s">
-        <v>499</v>
       </c>
       <c r="C5">
         <v>14.14</v>
@@ -3679,36 +3695,36 @@
         <v>14.14</v>
       </c>
       <c r="E5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F5" s="1">
         <v>45893</v>
       </c>
       <c r="G5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H5" t="s">
+        <v>500</v>
+      </c>
+      <c r="I5" t="s">
         <v>501</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>502</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>503</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>504</v>
-      </c>
-      <c r="L5" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>505</v>
+      </c>
+      <c r="B6" t="s">
         <v>506</v>
-      </c>
-      <c r="B6" t="s">
-        <v>507</v>
       </c>
       <c r="C6">
         <v>14.15</v>
@@ -3717,28 +3733,28 @@
         <v>14.15</v>
       </c>
       <c r="E6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F6" s="1">
         <v>45894</v>
       </c>
       <c r="G6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H6" t="s">
+        <v>508</v>
+      </c>
+      <c r="I6" t="s">
         <v>509</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>510</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>511</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>512</v>
-      </c>
-      <c r="L6" t="s">
-        <v>513</v>
       </c>
     </row>
   </sheetData>
@@ -3761,10 +3777,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B1" t="s">
         <v>514</v>
-      </c>
-      <c r="B1" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3795,10 +3811,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B1" t="s">
         <v>516</v>
-      </c>
-      <c r="B1" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3830,48 +3846,48 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B1" t="s">
         <v>518</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>519</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>520</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>521</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>522</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>523</v>
-      </c>
-      <c r="G1" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B2" s="1">
         <v>45895</v>
       </c>
       <c r="C2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D2" t="s">
         <v>526</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>527</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>528</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>529</v>
-      </c>
-      <c r="G2" t="s">
-        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -3896,69 +3912,69 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" t="s">
         <v>120</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>121</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>122</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>123</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>124</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>125</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>126</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>127</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>128</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>129</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>130</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>131</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>132</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>133</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>134</v>
-      </c>
-      <c r="P1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B2" t="s">
         <v>531</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>532</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>533</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>534</v>
-      </c>
-      <c r="E2" t="s">
-        <v>535</v>
       </c>
       <c r="F2">
         <v>15.11</v>
@@ -4245,25 +4261,25 @@
   <sheetData>
     <row r="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" t="s">
         <v>85</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>86</v>
       </c>
-      <c r="C1" t="s">
-        <v>87</v>
-      </c>
       <c r="D1" t="s">
+        <v>535</v>
+      </c>
+      <c r="E1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" t="s">
         <v>536</v>
       </c>
-      <c r="E1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F1" t="s">
-        <v>537</v>
-      </c>
       <c r="G1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
@@ -4278,97 +4294,97 @@
         <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N1" t="s">
+        <v>537</v>
+      </c>
+      <c r="O1" t="s">
+        <v>239</v>
+      </c>
+      <c r="P1" t="s">
         <v>538</v>
-      </c>
-      <c r="O1" t="s">
-        <v>240</v>
-      </c>
-      <c r="P1" t="s">
-        <v>539</v>
       </c>
       <c r="Q1" t="s">
         <v>6</v>
       </c>
       <c r="R1" t="s">
+        <v>539</v>
+      </c>
+      <c r="S1" t="s">
         <v>540</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>541</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>542</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>543</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>544</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>545</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>546</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>547</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>548</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>549</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
+        <v>346</v>
+      </c>
+      <c r="AD1" t="s">
         <v>550</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>347</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>551</v>
       </c>
       <c r="AE1" t="s">
         <v>46</v>
       </c>
       <c r="AF1" t="s">
+        <v>551</v>
+      </c>
+      <c r="AG1" t="s">
         <v>552</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>553</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>554</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>555</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>556</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>557</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>558</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>559</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>560</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>561</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>562</v>
       </c>
       <c r="AQ1" t="s">
         <v>13</v>
@@ -4383,49 +4399,49 @@
         <v>16</v>
       </c>
       <c r="AU1" t="s">
+        <v>562</v>
+      </c>
+      <c r="AV1" t="s">
         <v>563</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>564</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>565</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>566</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>567</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>568</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>569</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>570</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>571</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>572</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
+        <v>111</v>
+      </c>
+      <c r="BG1" t="s">
         <v>573</v>
       </c>
-      <c r="BF1" t="s">
-        <v>112</v>
-      </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>574</v>
       </c>
-      <c r="BH1" t="s">
-        <v>575</v>
-      </c>
       <c r="BI1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:61" x14ac:dyDescent="0.25">
@@ -4526,7 +4542,7 @@
         <v>1</v>
       </c>
       <c r="AG2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AH2">
         <v>0.46</v>
@@ -4646,19 +4662,19 @@
         <v>35</v>
       </c>
       <c r="B1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C1" t="s">
         <v>577</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>578</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>579</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>580</v>
-      </c>
-      <c r="F1" t="s">
-        <v>581</v>
       </c>
       <c r="G1" t="s">
         <v>32</v>
@@ -4667,16 +4683,16 @@
         <v>31</v>
       </c>
       <c r="I1" t="s">
+        <v>581</v>
+      </c>
+      <c r="J1" t="s">
         <v>582</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>583</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>584</v>
-      </c>
-      <c r="L1" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -4684,19 +4700,19 @@
         <v>59</v>
       </c>
       <c r="B2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C2" t="s">
         <v>586</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>587</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>588</v>
       </c>
-      <c r="E2" t="s">
-        <v>589</v>
-      </c>
       <c r="F2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G2" t="s">
         <v>56</v>
@@ -4705,10 +4721,10 @@
         <v>55</v>
       </c>
       <c r="I2" t="s">
+        <v>589</v>
+      </c>
+      <c r="J2" t="s">
         <v>590</v>
-      </c>
-      <c r="J2" t="s">
-        <v>591</v>
       </c>
       <c r="K2" t="s">
         <v>49</v>
@@ -4750,19 +4766,19 @@
         <v>35</v>
       </c>
       <c r="B1" t="s">
+        <v>576</v>
+      </c>
+      <c r="C1" t="s">
         <v>577</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>578</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>579</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>580</v>
-      </c>
-      <c r="F1" t="s">
-        <v>581</v>
       </c>
       <c r="G1" t="s">
         <v>32</v>
@@ -4771,16 +4787,16 @@
         <v>31</v>
       </c>
       <c r="I1" t="s">
+        <v>581</v>
+      </c>
+      <c r="J1" t="s">
         <v>582</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>583</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>584</v>
-      </c>
-      <c r="L1" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -4788,19 +4804,19 @@
         <v>59</v>
       </c>
       <c r="B2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C2" t="s">
         <v>586</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>587</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>588</v>
       </c>
-      <c r="E2" t="s">
-        <v>589</v>
-      </c>
       <c r="F2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G2" t="s">
         <v>56</v>
@@ -4809,16 +4825,16 @@
         <v>55</v>
       </c>
       <c r="I2" t="s">
+        <v>589</v>
+      </c>
+      <c r="J2" t="s">
         <v>590</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>591</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>592</v>
-      </c>
-      <c r="L2" t="s">
-        <v>593</v>
       </c>
     </row>
   </sheetData>
@@ -4842,68 +4858,68 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1" t="s">
         <v>594</v>
       </c>
-      <c r="B1" t="s">
-        <v>595</v>
-      </c>
       <c r="C1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B2" t="s">
         <v>596</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>597</v>
-      </c>
-      <c r="C2" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>598</v>
+      </c>
+      <c r="B3" t="s">
         <v>599</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>600</v>
-      </c>
-      <c r="C3" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>601</v>
+      </c>
+      <c r="B4" t="s">
         <v>602</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>603</v>
-      </c>
-      <c r="C4" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>604</v>
+      </c>
+      <c r="B5" t="s">
         <v>605</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>606</v>
-      </c>
-      <c r="C5" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>607</v>
+      </c>
+      <c r="B6" t="s">
         <v>608</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>609</v>
-      </c>
-      <c r="C6" t="s">
-        <v>610</v>
       </c>
     </row>
   </sheetData>
@@ -4923,7 +4939,7 @@
     <col min="1" max="1" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -4996,139 +5012,139 @@
         <v>71</v>
       </c>
       <c r="D1" t="s">
+        <v>615</v>
+      </c>
+      <c r="E1" t="s">
         <v>72</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>73</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>74</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>75</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>76</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>77</v>
-      </c>
-      <c r="J1" t="s">
-        <v>78</v>
       </c>
       <c r="K1" t="s">
         <v>39</v>
       </c>
       <c r="L1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M1" t="s">
         <v>79</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>80</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>81</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>82</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>83</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>84</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>85</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
+        <v>610</v>
+      </c>
+      <c r="U1" t="s">
+        <v>611</v>
+      </c>
+      <c r="V1" t="s">
         <v>86</v>
       </c>
-      <c r="T1" t="s">
-        <v>611</v>
-      </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
+        <v>535</v>
+      </c>
+      <c r="X1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>613</v>
+      </c>
+      <c r="AC1" t="s">
         <v>612</v>
-      </c>
-      <c r="V1" t="s">
-        <v>87</v>
-      </c>
-      <c r="W1" t="s">
-        <v>536</v>
-      </c>
-      <c r="X1" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>614</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>613</v>
       </c>
       <c r="AD1" t="s">
         <v>44</v>
       </c>
       <c r="AE1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF1" t="s">
         <v>92</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>93</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>94</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>95</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>96</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>97</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>98</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>99</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>100</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>101</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>102</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>103</v>
       </c>
-      <c r="AQ1" t="s">
-        <v>104</v>
-      </c>
       <c r="AR1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AS1" t="s">
         <v>106</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>107</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>108</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>109</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>110</v>
       </c>
       <c r="AW1" t="s">
         <v>7</v>
@@ -5143,76 +5159,76 @@
         <v>10</v>
       </c>
       <c r="BA1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BB1" t="s">
+        <v>112</v>
+      </c>
+      <c r="BC1" t="s">
         <v>113</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>114</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>115</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>116</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>117</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>118</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>119</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>120</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>121</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>122</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>123</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>124</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>125</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>126</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>127</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>128</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>129</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>130</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>131</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>132</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>133</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>134</v>
-      </c>
-      <c r="BX1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:76" x14ac:dyDescent="0.25">
@@ -5220,19 +5236,19 @@
         <v>45849</v>
       </c>
       <c r="B2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>616</v>
+      </c>
+      <c r="E2" t="s">
         <v>137</v>
       </c>
-      <c r="D2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>138</v>
-      </c>
-      <c r="F2" t="s">
-        <v>139</v>
       </c>
       <c r="G2" t="s">
         <v>57</v>
@@ -5241,25 +5257,25 @@
         <v>57</v>
       </c>
       <c r="I2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K2" t="s">
         <v>140</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>141</v>
       </c>
-      <c r="L2" t="s">
-        <v>142</v>
-      </c>
       <c r="M2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N2">
         <v>1</v>
       </c>
       <c r="O2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P2">
         <v>1.123</v>
@@ -5316,7 +5332,7 @@
         <v>3.15</v>
       </c>
       <c r="AH2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AI2">
         <v>1.02</v>
@@ -5325,7 +5341,7 @@
         <v>2.86</v>
       </c>
       <c r="AK2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AL2">
         <v>1.07</v>
@@ -5334,7 +5350,7 @@
         <v>3.01</v>
       </c>
       <c r="AN2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AO2">
         <v>1.23</v>
@@ -5346,13 +5362,13 @@
         <v>57</v>
       </c>
       <c r="AR2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AS2" t="s">
         <v>145</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
         <v>146</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>147</v>
       </c>
       <c r="AU2">
         <v>265.27999999999997</v>
@@ -5382,34 +5398,34 @@
         <v>299.77</v>
       </c>
       <c r="BD2" t="s">
+        <v>147</v>
+      </c>
+      <c r="BE2" t="s">
         <v>148</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>149</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>150</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>151</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>152</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>153</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>154</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>155</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BM2" t="s">
         <v>156</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>157</v>
       </c>
       <c r="BN2">
         <v>1.28</v>
@@ -5450,19 +5466,19 @@
         <v>45849</v>
       </c>
       <c r="B3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" t="s">
         <v>158</v>
       </c>
-      <c r="C3" t="s">
-        <v>159</v>
-      </c>
       <c r="D3" t="s">
-        <v>158</v>
+        <v>616</v>
       </c>
       <c r="E3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" t="s">
         <v>138</v>
-      </c>
-      <c r="F3" t="s">
-        <v>139</v>
       </c>
       <c r="G3" t="s">
         <v>57</v>
@@ -5471,25 +5487,25 @@
         <v>57</v>
       </c>
       <c r="I3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J3" t="s">
+        <v>139</v>
+      </c>
+      <c r="K3" t="s">
         <v>159</v>
       </c>
-      <c r="J3" t="s">
-        <v>140</v>
-      </c>
-      <c r="K3" t="s">
-        <v>160</v>
-      </c>
       <c r="L3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N3">
         <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P3">
         <v>1.1240000000000001</v>
@@ -5546,7 +5562,7 @@
         <v>3.18</v>
       </c>
       <c r="AH3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AI3">
         <v>1.03</v>
@@ -5555,7 +5571,7 @@
         <v>2.9</v>
       </c>
       <c r="AK3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AL3">
         <v>1.08</v>
@@ -5564,7 +5580,7 @@
         <v>3</v>
       </c>
       <c r="AN3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AO3">
         <v>1.24</v>
@@ -5576,13 +5592,13 @@
         <v>57</v>
       </c>
       <c r="AR3" t="s">
+        <v>144</v>
+      </c>
+      <c r="AS3" t="s">
         <v>145</v>
       </c>
-      <c r="AS3" t="s">
+      <c r="AT3" t="s">
         <v>146</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>147</v>
       </c>
       <c r="AU3">
         <v>265.48</v>
@@ -5612,34 +5628,34 @@
         <v>299.99</v>
       </c>
       <c r="BD3" t="s">
+        <v>161</v>
+      </c>
+      <c r="BE3" t="s">
         <v>162</v>
       </c>
-      <c r="BE3" t="s">
+      <c r="BF3" t="s">
         <v>163</v>
       </c>
-      <c r="BF3" t="s">
+      <c r="BG3" t="s">
         <v>164</v>
       </c>
-      <c r="BG3" t="s">
+      <c r="BH3" t="s">
         <v>165</v>
       </c>
-      <c r="BH3" t="s">
+      <c r="BI3" t="s">
         <v>166</v>
       </c>
-      <c r="BI3" t="s">
+      <c r="BJ3" t="s">
         <v>167</v>
       </c>
-      <c r="BJ3" t="s">
+      <c r="BK3" t="s">
         <v>168</v>
       </c>
-      <c r="BK3" t="s">
+      <c r="BL3" t="s">
         <v>169</v>
       </c>
-      <c r="BL3" t="s">
+      <c r="BM3" t="s">
         <v>170</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>171</v>
       </c>
       <c r="BN3">
         <v>1.29</v>
@@ -5680,19 +5696,19 @@
         <v>45849</v>
       </c>
       <c r="B4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" t="s">
         <v>172</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>616</v>
+      </c>
+      <c r="E4" t="s">
         <v>173</v>
       </c>
-      <c r="D4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" t="s">
-        <v>174</v>
-      </c>
       <c r="F4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G4" t="s">
         <v>57</v>
@@ -5701,25 +5717,25 @@
         <v>57</v>
       </c>
       <c r="I4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N4">
         <v>1</v>
       </c>
       <c r="O4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P4">
         <v>1.1259999999999999</v>
@@ -5776,7 +5792,7 @@
         <v>1.29</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AI4">
         <v>1.04</v>
@@ -5785,7 +5801,7 @@
         <v>1.17</v>
       </c>
       <c r="AK4" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AL4">
         <v>1.0900000000000001</v>
@@ -5794,7 +5810,7 @@
         <v>1.22</v>
       </c>
       <c r="AN4" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AO4">
         <v>1.25</v>
@@ -5806,13 +5822,13 @@
         <v>57</v>
       </c>
       <c r="AR4" t="s">
+        <v>177</v>
+      </c>
+      <c r="AS4" t="s">
         <v>178</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>179</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>180</v>
       </c>
       <c r="AU4" s="2">
         <v>106.43</v>
@@ -5842,34 +5858,34 @@
         <v>136.22999999999999</v>
       </c>
       <c r="BD4" t="s">
+        <v>180</v>
+      </c>
+      <c r="BE4" t="s">
         <v>181</v>
       </c>
-      <c r="BE4" t="s">
+      <c r="BF4" t="s">
         <v>182</v>
       </c>
-      <c r="BF4" t="s">
+      <c r="BG4" t="s">
         <v>183</v>
       </c>
-      <c r="BG4" t="s">
+      <c r="BH4" t="s">
         <v>184</v>
       </c>
-      <c r="BH4" t="s">
+      <c r="BI4" t="s">
         <v>185</v>
       </c>
-      <c r="BI4" t="s">
+      <c r="BJ4" t="s">
         <v>186</v>
       </c>
-      <c r="BJ4" t="s">
+      <c r="BK4" t="s">
         <v>187</v>
       </c>
-      <c r="BK4" t="s">
+      <c r="BL4" t="s">
         <v>188</v>
       </c>
-      <c r="BL4" t="s">
+      <c r="BM4" t="s">
         <v>189</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>190</v>
       </c>
       <c r="BN4">
         <v>1.31</v>
@@ -5910,82 +5926,82 @@
         <v>45849</v>
       </c>
       <c r="B5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" t="s">
         <v>191</v>
       </c>
-      <c r="C5" t="s">
-        <v>192</v>
-      </c>
       <c r="D5" t="s">
-        <v>191</v>
+        <v>617</v>
       </c>
       <c r="E5" s="6">
         <v>8967</v>
       </c>
       <c r="F5" t="s">
-        <v>139</v>
-      </c>
-      <c r="G5">
+        <v>138</v>
+      </c>
+      <c r="G5" s="6">
         <v>1</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="6">
         <v>1</v>
       </c>
       <c r="I5" t="s">
+        <v>192</v>
+      </c>
+      <c r="J5" t="s">
         <v>193</v>
       </c>
-      <c r="J5" t="s">
-        <v>208</v>
-      </c>
       <c r="K5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N5">
         <v>1</v>
       </c>
       <c r="O5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5">
         <v>500.14</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>500.14</v>
       </c>
       <c r="Z5">
         <v>250.14</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>250.14</v>
       </c>
       <c r="AB5" s="5">
         <v>0</v>
@@ -5997,133 +6013,133 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF5">
-        <v>1.1599999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AI5">
         <v>1.05</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AL5">
         <v>1.21</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AO5">
         <v>1.26</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AQ5">
         <v>0</v>
       </c>
       <c r="AR5" t="s">
+        <v>144</v>
+      </c>
+      <c r="AS5" t="s">
         <v>145</v>
       </c>
-      <c r="AS5" t="s">
+      <c r="AT5" t="s">
         <v>146</v>
       </c>
-      <c r="AT5" t="s">
-        <v>147</v>
-      </c>
       <c r="AU5">
-        <v>0</v>
+        <v>239.1</v>
       </c>
       <c r="AV5">
         <v>12</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>14.35</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>14.35</v>
       </c>
       <c r="AY5">
         <v>0</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>31.09</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>270.19</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>270.19</v>
       </c>
       <c r="BD5" t="s">
+        <v>197</v>
+      </c>
+      <c r="BE5" t="s">
         <v>198</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BF5" t="s">
         <v>199</v>
       </c>
-      <c r="BF5" t="s">
+      <c r="BG5" t="s">
         <v>200</v>
       </c>
-      <c r="BG5" t="s">
+      <c r="BH5" t="s">
         <v>201</v>
       </c>
-      <c r="BH5" t="s">
-        <v>209</v>
-      </c>
       <c r="BI5" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="BJ5" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="BK5" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="BL5" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="BM5" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="BN5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO5">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BP5">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BQ5">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BR5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BS5" s="1">
-        <v>45862</v>
+        <v>45859</v>
       </c>
       <c r="BT5" s="1">
-        <v>45863</v>
+        <v>45860</v>
       </c>
       <c r="BU5" s="1">
-        <v>45864</v>
+        <v>45861</v>
       </c>
       <c r="BV5" s="6">
         <v>1</v>
@@ -6140,82 +6156,82 @@
         <v>45849</v>
       </c>
       <c r="B6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" t="s">
         <v>191</v>
       </c>
-      <c r="C6" t="s">
-        <v>192</v>
-      </c>
       <c r="D6" t="s">
-        <v>191</v>
+        <v>617</v>
       </c>
       <c r="E6" s="6">
         <v>8967</v>
       </c>
       <c r="F6" t="s">
-        <v>139</v>
-      </c>
-      <c r="G6">
+        <v>138</v>
+      </c>
+      <c r="G6" s="6">
         <v>1</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="6">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J6" t="s">
+        <v>207</v>
+      </c>
+      <c r="K6" t="s">
         <v>194</v>
       </c>
-      <c r="K6" t="s">
-        <v>195</v>
-      </c>
       <c r="L6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N6">
         <v>1</v>
       </c>
       <c r="O6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
         <v>1</v>
       </c>
-      <c r="Q6">
+      <c r="U6">
         <v>1</v>
       </c>
-      <c r="R6">
+      <c r="V6">
         <v>1</v>
       </c>
-      <c r="S6">
+      <c r="W6">
         <v>1</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
       </c>
       <c r="X6">
         <v>500.14</v>
       </c>
       <c r="Y6">
-        <v>500.14</v>
+        <v>0</v>
       </c>
       <c r="Z6">
         <v>250.14</v>
       </c>
       <c r="AA6">
-        <v>250.14</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="5">
         <v>0</v>
@@ -6227,133 +6243,133 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="AE6">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="AG6">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AI6">
         <v>1.05</v>
       </c>
       <c r="AJ6">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AL6">
         <v>1.21</v>
       </c>
       <c r="AM6">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AO6">
         <v>1.26</v>
       </c>
       <c r="AP6">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AQ6">
         <v>0</v>
       </c>
       <c r="AR6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AS6" t="s">
         <v>145</v>
       </c>
-      <c r="AS6" t="s">
+      <c r="AT6" t="s">
         <v>146</v>
       </c>
-      <c r="AT6" t="s">
-        <v>147</v>
-      </c>
       <c r="AU6">
-        <v>239.1</v>
+        <v>0</v>
       </c>
       <c r="AV6">
         <v>12</v>
       </c>
       <c r="AW6">
-        <v>14.35</v>
+        <v>0</v>
       </c>
       <c r="AX6">
-        <v>14.35</v>
+        <v>0</v>
       </c>
       <c r="AY6">
         <v>0</v>
       </c>
       <c r="AZ6">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BA6">
-        <v>31.09</v>
+        <v>0</v>
       </c>
       <c r="BB6">
-        <v>270.19</v>
+        <v>0</v>
       </c>
       <c r="BC6">
-        <v>270.19</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="s">
+        <v>197</v>
+      </c>
+      <c r="BE6" t="s">
         <v>198</v>
       </c>
-      <c r="BE6" t="s">
+      <c r="BF6" t="s">
         <v>199</v>
       </c>
-      <c r="BF6" t="s">
+      <c r="BG6" t="s">
         <v>200</v>
       </c>
-      <c r="BG6" t="s">
-        <v>201</v>
-      </c>
       <c r="BH6" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="BI6" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="BJ6" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="BK6" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="BL6" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="BM6" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="BN6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BO6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="BP6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BQ6">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BR6">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BS6" s="1">
-        <v>45859</v>
+        <v>45862</v>
       </c>
       <c r="BT6" s="1">
-        <v>45860</v>
+        <v>45863</v>
       </c>
       <c r="BU6" s="1">
-        <v>45861</v>
+        <v>45864</v>
       </c>
       <c r="BV6" s="6">
         <v>1</v>
@@ -6370,19 +6386,19 @@
         <v>45849</v>
       </c>
       <c r="B7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" t="s">
         <v>215</v>
       </c>
-      <c r="C7" t="s">
-        <v>216</v>
-      </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>618</v>
       </c>
       <c r="E7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G7" t="s">
         <v>53</v>
@@ -6391,25 +6407,25 @@
         <v>57</v>
       </c>
       <c r="I7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K7" t="s">
         <v>62</v>
       </c>
       <c r="L7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N7">
         <v>1</v>
       </c>
       <c r="O7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P7">
         <v>1.1200000000000001</v>
@@ -6466,7 +6482,7 @@
         <v>3.28</v>
       </c>
       <c r="AH7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AI7">
         <v>1.06</v>
@@ -6475,7 +6491,7 @@
         <v>1.06</v>
       </c>
       <c r="AK7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL7">
         <v>1.22</v>
@@ -6484,7 +6500,7 @@
         <v>1.22</v>
       </c>
       <c r="AN7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AO7">
         <v>1.27</v>
@@ -6496,13 +6512,13 @@
         <v>57</v>
       </c>
       <c r="AR7" t="s">
+        <v>177</v>
+      </c>
+      <c r="AS7" t="s">
         <v>178</v>
       </c>
-      <c r="AS7" t="s">
+      <c r="AT7" t="s">
         <v>179</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>180</v>
       </c>
       <c r="AU7">
         <v>267.95999999999998</v>
@@ -6532,34 +6548,34 @@
         <v>343</v>
       </c>
       <c r="BD7" t="s">
+        <v>219</v>
+      </c>
+      <c r="BE7" t="s">
         <v>220</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="BF7" t="s">
         <v>221</v>
       </c>
-      <c r="BF7" t="s">
+      <c r="BG7" t="s">
         <v>222</v>
       </c>
-      <c r="BG7" t="s">
+      <c r="BH7" t="s">
         <v>223</v>
       </c>
-      <c r="BH7" t="s">
+      <c r="BI7" t="s">
         <v>224</v>
       </c>
-      <c r="BI7" t="s">
+      <c r="BJ7" t="s">
         <v>225</v>
       </c>
-      <c r="BJ7" t="s">
+      <c r="BK7" t="s">
         <v>226</v>
       </c>
-      <c r="BK7" t="s">
+      <c r="BL7" t="s">
         <v>227</v>
       </c>
-      <c r="BL7" t="s">
+      <c r="BM7" t="s">
         <v>228</v>
-      </c>
-      <c r="BM7" t="s">
-        <v>229</v>
       </c>
       <c r="BN7">
         <v>1.34</v>
@@ -6595,8 +6611,11 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="7"/>
+    </row>
     <row r="10" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D10" s="7"/>
       <c r="AA10" s="3">
         <f t="shared" ref="AA10:AA15" si="0">Z2*R2</f>
         <v>280.87353000000002</v>
@@ -6639,6 +6658,7 @@
       </c>
     </row>
     <row r="11" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="7"/>
       <c r="AA11" s="3">
         <f t="shared" si="0"/>
         <v>281.13488000000001</v>
@@ -6681,6 +6701,7 @@
       </c>
     </row>
     <row r="12" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="7"/>
       <c r="AA12" s="3">
         <f t="shared" si="0"/>
         <v>112.74637999999999</v>
@@ -6723,90 +6744,93 @@
       </c>
     </row>
     <row r="13" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="7"/>
       <c r="AA13" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>250.14</v>
       </c>
       <c r="AE13" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.776554</v>
       </c>
       <c r="AG13" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8766099999999999</v>
       </c>
       <c r="AJ13" s="3">
         <f>$R5*AI5</f>
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AM13" s="3">
         <f>$R5*AL5</f>
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP13" s="3">
         <f>($AA13-AJ13-AM13)*AO5%</f>
-        <v>0</v>
+        <v>3.1232879999999996</v>
       </c>
       <c r="AS13" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11.036452000000001</v>
       </c>
       <c r="AU13" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>239.10354799999999</v>
       </c>
       <c r="BA13" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>31.08242576</v>
       </c>
       <c r="BB13" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>270.19</v>
       </c>
     </row>
     <row r="14" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="7"/>
       <c r="AA14" s="3">
         <f t="shared" si="0"/>
-        <v>250.14</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="3">
         <f t="shared" si="5"/>
-        <v>2.776554</v>
+        <v>0</v>
       </c>
       <c r="AG14" s="3">
         <f t="shared" si="5"/>
-        <v>2.8766099999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ14" s="3">
         <f>$R6*AI6</f>
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AM14" s="3">
         <f>$R6*AL6</f>
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP14" s="3">
         <f>($AA14-AJ14-AM14)*AO6%</f>
-        <v>3.1232879999999996</v>
+        <v>0</v>
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="1"/>
-        <v>11.036452000000001</v>
+        <v>0</v>
       </c>
       <c r="AU14" s="3">
         <f t="shared" si="2"/>
-        <v>239.10354799999999</v>
+        <v>0</v>
       </c>
       <c r="BA14" s="3">
         <f t="shared" si="3"/>
-        <v>31.08242576</v>
+        <v>0</v>
       </c>
       <c r="BB14" s="3">
         <f t="shared" si="4"/>
-        <v>270.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D15" s="7"/>
       <c r="AA15" s="3">
         <f t="shared" si="0"/>
         <v>280.16800000000001</v>
@@ -6848,8 +6872,11 @@
         <v>342.99</v>
       </c>
     </row>
-    <row r="16" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="27:72" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="4:72" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D17" s="7"/>
       <c r="AA17" s="3">
         <f>SUM(AA10:AA15)</f>
         <v>1205.0627899999999</v>
@@ -6891,7 +6918,8 @@
         <v>1349.27</v>
       </c>
     </row>
-    <row r="18" spans="27:72" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:72" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D18" s="7"/>
       <c r="AA18" s="3">
         <f>SUM(AA2:AA7)</f>
         <v>1205.06</v>
@@ -6949,9 +6977,9 @@
         <v>1349.18</v>
       </c>
     </row>
-    <row r="28" spans="27:72" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:72" x14ac:dyDescent="0.25">
       <c r="BT28" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>
@@ -6988,69 +7016,69 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B1" t="s">
         <v>230</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>231</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>232</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>233</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>234</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>235</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>236</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>237</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>238</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>239</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>240</v>
       </c>
-      <c r="L1" t="s">
-        <v>241</v>
-      </c>
       <c r="M1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N1" t="s">
         <v>115</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>116</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>117</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>118</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D2" t="s">
         <v>242</v>
-      </c>
-      <c r="C2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D2" t="s">
-        <v>243</v>
       </c>
       <c r="E2" s="2">
         <v>1144.25</v>
@@ -7077,33 +7105,33 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
+        <v>243</v>
+      </c>
+      <c r="N2" t="s">
         <v>244</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>245</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>246</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>247</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D3" t="s">
         <v>249</v>
-      </c>
-      <c r="C3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D3" t="s">
-        <v>250</v>
       </c>
       <c r="E3">
         <v>1205.06</v>
@@ -7130,33 +7158,33 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
+        <v>250</v>
+      </c>
+      <c r="N3" t="s">
         <v>251</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>252</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>253</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>254</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E4" s="2">
         <v>1144.25</v>
@@ -7183,33 +7211,33 @@
         <v>18.77</v>
       </c>
       <c r="M4" t="s">
+        <v>256</v>
+      </c>
+      <c r="N4" t="s">
         <v>257</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>258</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>259</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>260</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C5" t="s">
+        <v>261</v>
+      </c>
+      <c r="D5" t="s">
         <v>262</v>
-      </c>
-      <c r="C5" t="s">
-        <v>262</v>
-      </c>
-      <c r="D5" t="s">
-        <v>263</v>
       </c>
       <c r="E5" s="2">
         <v>1349.18</v>
@@ -7236,33 +7264,33 @@
         <v>22.26</v>
       </c>
       <c r="M5" t="s">
+        <v>263</v>
+      </c>
+      <c r="N5" t="s">
         <v>264</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>265</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>266</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>267</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" t="s">
         <v>269</v>
-      </c>
-      <c r="C6" t="s">
-        <v>269</v>
-      </c>
-      <c r="D6" t="s">
-        <v>270</v>
       </c>
       <c r="E6" s="2">
         <v>1346.33</v>
@@ -7289,19 +7317,19 @@
         <v>22.35</v>
       </c>
       <c r="M6" t="s">
+        <v>270</v>
+      </c>
+      <c r="N6" t="s">
         <v>271</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>272</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>273</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>274</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -7453,46 +7481,46 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" t="s">
         <v>231</v>
       </c>
-      <c r="B1" t="s">
-        <v>232</v>
-      </c>
       <c r="C1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" t="s">
         <v>73</v>
       </c>
-      <c r="D1" t="s">
-        <v>74</v>
-      </c>
       <c r="E1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K1" t="s">
         <v>106</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>107</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>108</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>109</v>
-      </c>
-      <c r="N1" t="s">
-        <v>110</v>
       </c>
       <c r="O1" t="s">
         <v>7</v>
@@ -7507,45 +7535,45 @@
         <v>10</v>
       </c>
       <c r="S1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="T1" t="s">
+        <v>112</v>
+      </c>
+      <c r="U1" t="s">
         <v>113</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>114</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>115</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>116</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>117</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>118</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C2" t="s">
         <v>277</v>
       </c>
-      <c r="B2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>278</v>
       </c>
-      <c r="D2" t="s">
-        <v>279</v>
-      </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -7560,13 +7588,13 @@
         <v>1.49</v>
       </c>
       <c r="J2" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2" t="s">
         <v>280</v>
       </c>
-      <c r="K2" t="s">
-        <v>281</v>
-      </c>
       <c r="L2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M2">
         <v>1.49</v>
@@ -7596,36 +7624,36 @@
         <v>1.52</v>
       </c>
       <c r="V2" t="s">
+        <v>281</v>
+      </c>
+      <c r="W2" t="s">
         <v>282</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>283</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>284</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>285</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -7640,13 +7668,13 @@
         <v>1.45</v>
       </c>
       <c r="J3" t="s">
+        <v>177</v>
+      </c>
+      <c r="K3" t="s">
         <v>178</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>179</v>
-      </c>
-      <c r="L3" t="s">
-        <v>180</v>
       </c>
       <c r="M3">
         <v>1.45</v>
@@ -7676,36 +7704,36 @@
         <v>1.86</v>
       </c>
       <c r="V3" t="s">
+        <v>287</v>
+      </c>
+      <c r="W3" t="s">
         <v>288</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>289</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>290</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>291</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C4" t="s">
         <v>293</v>
       </c>
-      <c r="B4" t="s">
-        <v>293</v>
-      </c>
-      <c r="C4" t="s">
-        <v>294</v>
-      </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -7720,13 +7748,13 @@
         <v>1.46</v>
       </c>
       <c r="J4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K4" t="s">
+        <v>145</v>
+      </c>
+      <c r="L4" t="s">
         <v>146</v>
-      </c>
-      <c r="L4" t="s">
-        <v>147</v>
       </c>
       <c r="M4">
         <v>1.46</v>
@@ -7756,36 +7784,36 @@
         <v>1.65</v>
       </c>
       <c r="V4" t="s">
+        <v>295</v>
+      </c>
+      <c r="W4" t="s">
         <v>296</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>297</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>298</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>299</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C5" t="s">
         <v>301</v>
       </c>
-      <c r="B5" t="s">
-        <v>301</v>
-      </c>
-      <c r="C5" t="s">
-        <v>302</v>
-      </c>
       <c r="D5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -7800,13 +7828,13 @@
         <v>1.47</v>
       </c>
       <c r="J5" t="s">
+        <v>302</v>
+      </c>
+      <c r="K5" t="s">
         <v>303</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>304</v>
-      </c>
-      <c r="L5" t="s">
-        <v>305</v>
       </c>
       <c r="M5">
         <v>1.47</v>
@@ -7836,36 +7864,36 @@
         <v>2.11</v>
       </c>
       <c r="V5" t="s">
+        <v>305</v>
+      </c>
+      <c r="W5" t="s">
         <v>306</v>
       </c>
-      <c r="W5" t="s">
+      <c r="X5" t="s">
         <v>307</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
         <v>308</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="Z5" t="s">
         <v>309</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>310</v>
+      </c>
+      <c r="B6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" t="s">
         <v>311</v>
       </c>
-      <c r="B6" t="s">
-        <v>311</v>
-      </c>
-      <c r="C6" t="s">
-        <v>312</v>
-      </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -7880,13 +7908,13 @@
         <v>1.48</v>
       </c>
       <c r="J6" t="s">
+        <v>312</v>
+      </c>
+      <c r="K6" t="s">
         <v>313</v>
       </c>
-      <c r="K6" t="s">
-        <v>314</v>
-      </c>
       <c r="L6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M6">
         <v>1.48</v>
@@ -7916,19 +7944,19 @@
         <v>1.53</v>
       </c>
       <c r="V6" t="s">
+        <v>314</v>
+      </c>
+      <c r="W6" t="s">
         <v>315</v>
       </c>
-      <c r="W6" t="s">
+      <c r="X6" t="s">
         <v>316</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
         <v>317</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="Z6" t="s">
         <v>318</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -7972,73 +8000,73 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1" t="s">
         <v>320</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" t="s">
         <v>321</v>
       </c>
-      <c r="C1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F1" t="s">
         <v>322</v>
       </c>
-      <c r="E1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>323</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>324</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" t="s">
         <v>325</v>
       </c>
-      <c r="I1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>326</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>327</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>328</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>329</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>330</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>331</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>332</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>333</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>334</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>335</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>336</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>337</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>338</v>
-      </c>
-      <c r="W1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
@@ -8046,16 +8074,16 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D2">
         <v>0.75</v>
       </c>
       <c r="E2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -8079,7 +8107,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N2" t="s">
         <v>57</v>
@@ -8117,16 +8145,16 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D3">
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -8150,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N3" t="s">
         <v>57</v>
@@ -8188,16 +8216,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D4">
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -8221,7 +8249,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N4" t="s">
         <v>57</v>
@@ -8259,16 +8287,16 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D5">
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -8292,7 +8320,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N5" t="s">
         <v>57</v>
@@ -8330,16 +8358,16 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D6">
         <v>1.5</v>
       </c>
       <c r="E6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -8363,7 +8391,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N6" t="s">
         <v>57</v>
@@ -8401,16 +8429,16 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -8434,7 +8462,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N7" t="s">
         <v>57</v>
@@ -8472,16 +8500,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D8">
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -8505,7 +8533,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N8" t="s">
         <v>57</v>
@@ -8543,16 +8571,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D9">
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -8576,7 +8604,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N9" t="s">
         <v>57</v>
@@ -8614,16 +8642,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D10">
         <v>6</v>
       </c>
       <c r="E10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -8647,7 +8675,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N10" t="s">
         <v>57</v>
@@ -8685,16 +8713,16 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D11">
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -8718,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N11" t="s">
         <v>57</v>
@@ -8792,73 +8820,73 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1" t="s">
         <v>320</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" t="s">
         <v>321</v>
       </c>
-      <c r="C1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F1" t="s">
         <v>322</v>
       </c>
-      <c r="E1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>323</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>324</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" t="s">
         <v>325</v>
       </c>
-      <c r="I1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
+        <v>327</v>
+      </c>
+      <c r="L1" t="s">
+        <v>328</v>
+      </c>
+      <c r="M1" t="s">
         <v>326</v>
       </c>
-      <c r="K1" t="s">
-        <v>328</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>329</v>
       </c>
-      <c r="M1" t="s">
-        <v>327</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>330</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>331</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>332</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>333</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>334</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>335</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>336</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>337</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>338</v>
-      </c>
-      <c r="W1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
@@ -8866,16 +8894,16 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D2">
         <v>0.75</v>
       </c>
       <c r="E2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -8896,7 +8924,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M2">
         <v>0.01</v>
@@ -8937,16 +8965,16 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D3">
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -8967,7 +8995,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M3">
         <v>0.13</v>
@@ -9008,16 +9036,16 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D4">
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -9038,7 +9066,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M4">
         <v>0.09</v>
@@ -9079,16 +9107,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D5">
         <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -9109,7 +9137,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M5">
         <v>0.21</v>
@@ -9150,16 +9178,16 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D6">
         <v>1.5</v>
       </c>
       <c r="E6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -9180,7 +9208,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M6">
         <v>0.02</v>
@@ -9221,16 +9249,16 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -9251,7 +9279,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M7">
         <v>15.92</v>
@@ -9292,16 +9320,16 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D8">
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -9322,7 +9350,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M8">
         <v>15.93</v>
@@ -9363,16 +9391,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D9">
         <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -9393,7 +9421,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M9">
         <v>9.58</v>
@@ -9434,16 +9462,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D10">
         <v>6</v>
       </c>
       <c r="E10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -9464,7 +9492,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M10">
         <v>14.35</v>
@@ -9505,16 +9533,16 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D11">
         <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -9535,7 +9563,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M11">
         <v>24.12</v>
@@ -9612,73 +9640,73 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1" t="s">
         <v>320</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" t="s">
         <v>321</v>
       </c>
-      <c r="C1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F1" t="s">
         <v>322</v>
       </c>
-      <c r="E1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>323</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>324</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" t="s">
         <v>325</v>
       </c>
-      <c r="I1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>326</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>327</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>328</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>329</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>330</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>331</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>332</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>333</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>334</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>335</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>336</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>337</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>338</v>
-      </c>
-      <c r="W1" t="s">
-        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -9722,73 +9750,73 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1" t="s">
         <v>320</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" t="s">
         <v>321</v>
       </c>
-      <c r="C1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F1" t="s">
         <v>322</v>
       </c>
-      <c r="E1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>323</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>324</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J1" t="s">
         <v>325</v>
       </c>
-      <c r="I1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>326</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>327</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>328</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>329</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>330</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>331</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>332</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>333</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>334</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>335</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>336</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>337</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>338</v>
-      </c>
-      <c r="W1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
@@ -9796,16 +9824,16 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -9829,7 +9857,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N2" t="s">
         <v>57</v>
@@ -9867,16 +9895,16 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D3">
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -9900,7 +9928,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N3" t="s">
         <v>57</v>
@@ -9938,16 +9966,16 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -9971,7 +9999,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N4" t="s">
         <v>57</v>
@@ -10009,16 +10037,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D5">
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -10042,7 +10070,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N5" t="s">
         <v>57</v>
@@ -10080,16 +10108,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -10113,7 +10141,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N6" t="s">
         <v>57</v>
@@ -10151,16 +10179,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -10184,7 +10212,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N7" t="s">
         <v>57</v>
@@ -10222,16 +10250,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -10255,7 +10283,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N8" t="s">
         <v>57</v>
@@ -10293,16 +10321,16 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D9">
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -10326,7 +10354,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N9" t="s">
         <v>57</v>
@@ -10364,16 +10392,16 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -10397,7 +10425,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N10" t="s">
         <v>57</v>
@@ -10435,16 +10463,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D11">
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -10468,7 +10496,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="N11" t="s">
         <v>57</v>

--- a/src/main/resources/menuItems/Sales/Transactions/480464 - Sales Return with Invoice Reference-AC.xlsx
+++ b/src/main/resources/menuItems/Sales/Transactions/480464 - Sales Return with Invoice Reference-AC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\IdeaProjects\Wings-Automation\src\main\resources\menuItems\Sales\Transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77185577-FD6D-4B2D-A660-5EAA1B260204}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A13C3C1-4E32-441D-B3F6-2120CC5B5F85}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32760" yWindow="32760" windowWidth="32760" windowHeight="32760" tabRatio="938" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5950,7 +5950,7 @@
         <v>192</v>
       </c>
       <c r="J5" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="K5" t="s">
         <v>194</v>
@@ -5968,40 +5968,40 @@
         <v>142</v>
       </c>
       <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
         <v>1</v>
       </c>
-      <c r="Q5">
+      <c r="U5">
         <v>1</v>
       </c>
-      <c r="R5">
+      <c r="V5">
         <v>1</v>
       </c>
-      <c r="S5">
+      <c r="W5">
         <v>1</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
       </c>
       <c r="X5">
         <v>500.14</v>
       </c>
       <c r="Y5">
-        <v>500.14</v>
+        <v>0</v>
       </c>
       <c r="Z5">
         <v>250.14</v>
       </c>
       <c r="AA5">
-        <v>250.14</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="5">
         <v>0</v>
@@ -6013,13 +6013,13 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="AE5">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="AG5">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="s">
         <v>195</v>
@@ -6028,7 +6028,7 @@
         <v>1.05</v>
       </c>
       <c r="AJ5">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="s">
         <v>195</v>
@@ -6037,7 +6037,7 @@
         <v>1.21</v>
       </c>
       <c r="AM5">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="s">
         <v>196</v>
@@ -6046,7 +6046,7 @@
         <v>1.26</v>
       </c>
       <c r="AP5">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AQ5">
         <v>0</v>
@@ -6061,31 +6061,31 @@
         <v>146</v>
       </c>
       <c r="AU5">
-        <v>239.1</v>
+        <v>0</v>
       </c>
       <c r="AV5">
         <v>12</v>
       </c>
       <c r="AW5">
-        <v>14.35</v>
+        <v>0</v>
       </c>
       <c r="AX5">
-        <v>14.35</v>
+        <v>0</v>
       </c>
       <c r="AY5">
         <v>0</v>
       </c>
       <c r="AZ5">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BA5">
-        <v>31.09</v>
+        <v>0</v>
       </c>
       <c r="BB5">
-        <v>270.19</v>
+        <v>0</v>
       </c>
       <c r="BC5">
-        <v>270.19</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="s">
         <v>197</v>
@@ -6100,46 +6100,46 @@
         <v>200</v>
       </c>
       <c r="BH5" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="BI5" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="BJ5" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="BK5" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="BL5" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="BM5" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="BN5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BO5">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="BP5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BQ5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BR5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BS5" s="1">
-        <v>45859</v>
+        <v>45862</v>
       </c>
       <c r="BT5" s="1">
-        <v>45860</v>
+        <v>45863</v>
       </c>
       <c r="BU5" s="1">
-        <v>45861</v>
+        <v>45864</v>
       </c>
       <c r="BV5" s="6">
         <v>1</v>
@@ -6180,7 +6180,7 @@
         <v>192</v>
       </c>
       <c r="J6" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="K6" t="s">
         <v>194</v>
@@ -6198,40 +6198,40 @@
         <v>142</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6">
         <v>500.14</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>500.14</v>
       </c>
       <c r="Z6">
         <v>250.14</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>250.14</v>
       </c>
       <c r="AB6" s="5">
         <v>0</v>
@@ -6243,13 +6243,13 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF6">
-        <v>1.1599999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH6" t="s">
         <v>195</v>
@@ -6258,7 +6258,7 @@
         <v>1.05</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK6" t="s">
         <v>195</v>
@@ -6267,7 +6267,7 @@
         <v>1.21</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN6" t="s">
         <v>196</v>
@@ -6276,7 +6276,7 @@
         <v>1.26</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AQ6">
         <v>0</v>
@@ -6291,31 +6291,31 @@
         <v>146</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>239.1</v>
       </c>
       <c r="AV6">
         <v>12</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>14.35</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>14.35</v>
       </c>
       <c r="AY6">
         <v>0</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>31.09</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>270.19</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>270.19</v>
       </c>
       <c r="BD6" t="s">
         <v>197</v>
@@ -6330,46 +6330,46 @@
         <v>200</v>
       </c>
       <c r="BH6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="BI6" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="BJ6" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="BK6" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="BL6" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="BM6" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="BN6">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO6">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BP6">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BQ6">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BR6">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BS6" s="1">
-        <v>45862</v>
+        <v>45859</v>
       </c>
       <c r="BT6" s="1">
-        <v>45863</v>
+        <v>45860</v>
       </c>
       <c r="BU6" s="1">
-        <v>45864</v>
+        <v>45861</v>
       </c>
       <c r="BV6" s="6">
         <v>1</v>
@@ -6747,86 +6747,86 @@
       <c r="D13" s="7"/>
       <c r="AA13" s="3">
         <f t="shared" si="0"/>
-        <v>250.14</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="3">
         <f t="shared" si="5"/>
-        <v>2.776554</v>
+        <v>0</v>
       </c>
       <c r="AG13" s="3">
         <f t="shared" si="5"/>
-        <v>2.8766099999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ13" s="3">
         <f>$R5*AI5</f>
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AM13" s="3">
         <f>$R5*AL5</f>
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP13" s="3">
         <f>($AA13-AJ13-AM13)*AO5%</f>
-        <v>3.1232879999999996</v>
+        <v>0</v>
       </c>
       <c r="AS13" s="3">
         <f t="shared" si="1"/>
-        <v>11.036452000000001</v>
+        <v>0</v>
       </c>
       <c r="AU13" s="3">
         <f t="shared" si="2"/>
-        <v>239.10354799999999</v>
+        <v>0</v>
       </c>
       <c r="BA13" s="3">
         <f t="shared" si="3"/>
-        <v>31.08242576</v>
+        <v>0</v>
       </c>
       <c r="BB13" s="3">
         <f t="shared" si="4"/>
-        <v>270.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D14" s="7"/>
       <c r="AA14" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>250.14</v>
       </c>
       <c r="AE14" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.776554</v>
       </c>
       <c r="AG14" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8766099999999999</v>
       </c>
       <c r="AJ14" s="3">
         <f>$R6*AI6</f>
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AM14" s="3">
         <f>$R6*AL6</f>
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP14" s="3">
         <f>($AA14-AJ14-AM14)*AO6%</f>
-        <v>0</v>
+        <v>3.1232879999999996</v>
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11.036452000000001</v>
       </c>
       <c r="AU14" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>239.10354799999999</v>
       </c>
       <c r="BA14" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>31.08242576</v>
       </c>
       <c r="BB14" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>270.19</v>
       </c>
     </row>
     <row r="15" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">

--- a/src/main/resources/menuItems/Sales/Transactions/480464 - Sales Return with Invoice Reference-AC.xlsx
+++ b/src/main/resources/menuItems/Sales/Transactions/480464 - Sales Return with Invoice Reference-AC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\IdeaProjects\Wings-Automation\src\main\resources\menuItems\Sales\Transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A13C3C1-4E32-441D-B3F6-2120CC5B5F85}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6DAC46-8B8B-48F1-A9B4-AF5F47CDD76F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32760" yWindow="32760" windowWidth="32760" windowHeight="32760" tabRatio="938" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5950,7 +5950,7 @@
         <v>192</v>
       </c>
       <c r="J5" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="K5" t="s">
         <v>194</v>
@@ -5968,40 +5968,40 @@
         <v>142</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5">
         <v>500.14</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>500.14</v>
       </c>
       <c r="Z5">
         <v>250.14</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>250.14</v>
       </c>
       <c r="AB5" s="5">
         <v>0</v>
@@ -6013,13 +6013,13 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF5">
-        <v>1.1599999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH5" t="s">
         <v>195</v>
@@ -6028,7 +6028,7 @@
         <v>1.05</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="s">
         <v>195</v>
@@ -6037,7 +6037,7 @@
         <v>1.21</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN5" t="s">
         <v>196</v>
@@ -6046,7 +6046,7 @@
         <v>1.26</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AQ5">
         <v>0</v>
@@ -6061,31 +6061,31 @@
         <v>146</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>239.1</v>
       </c>
       <c r="AV5">
         <v>12</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>14.35</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>14.35</v>
       </c>
       <c r="AY5">
         <v>0</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>31.09</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>270.19</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>270.19</v>
       </c>
       <c r="BD5" t="s">
         <v>197</v>
@@ -6100,46 +6100,46 @@
         <v>200</v>
       </c>
       <c r="BH5" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="BI5" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="BJ5" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="BK5" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="BL5" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="BM5" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="BN5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO5">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BP5">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BQ5">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BR5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BS5" s="1">
-        <v>45862</v>
+        <v>45859</v>
       </c>
       <c r="BT5" s="1">
-        <v>45863</v>
+        <v>45860</v>
       </c>
       <c r="BU5" s="1">
-        <v>45864</v>
+        <v>45861</v>
       </c>
       <c r="BV5" s="6">
         <v>1</v>
@@ -6180,7 +6180,7 @@
         <v>192</v>
       </c>
       <c r="J6" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="K6" t="s">
         <v>194</v>
@@ -6198,40 +6198,40 @@
         <v>142</v>
       </c>
       <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
         <v>1</v>
       </c>
-      <c r="Q6">
+      <c r="U6">
         <v>1</v>
       </c>
-      <c r="R6">
+      <c r="V6">
         <v>1</v>
       </c>
-      <c r="S6">
+      <c r="W6">
         <v>1</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
       </c>
       <c r="X6">
         <v>500.14</v>
       </c>
       <c r="Y6">
-        <v>500.14</v>
+        <v>0</v>
       </c>
       <c r="Z6">
         <v>250.14</v>
       </c>
       <c r="AA6">
-        <v>250.14</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="5">
         <v>0</v>
@@ -6243,13 +6243,13 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="AE6">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="AG6">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="s">
         <v>195</v>
@@ -6258,7 +6258,7 @@
         <v>1.05</v>
       </c>
       <c r="AJ6">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="s">
         <v>195</v>
@@ -6267,7 +6267,7 @@
         <v>1.21</v>
       </c>
       <c r="AM6">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="s">
         <v>196</v>
@@ -6276,7 +6276,7 @@
         <v>1.26</v>
       </c>
       <c r="AP6">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AQ6">
         <v>0</v>
@@ -6291,31 +6291,31 @@
         <v>146</v>
       </c>
       <c r="AU6">
-        <v>239.1</v>
+        <v>0</v>
       </c>
       <c r="AV6">
         <v>12</v>
       </c>
       <c r="AW6">
-        <v>14.35</v>
+        <v>0</v>
       </c>
       <c r="AX6">
-        <v>14.35</v>
+        <v>0</v>
       </c>
       <c r="AY6">
         <v>0</v>
       </c>
       <c r="AZ6">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BA6">
-        <v>31.09</v>
+        <v>0</v>
       </c>
       <c r="BB6">
-        <v>270.19</v>
+        <v>0</v>
       </c>
       <c r="BC6">
-        <v>270.19</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="s">
         <v>197</v>
@@ -6330,46 +6330,46 @@
         <v>200</v>
       </c>
       <c r="BH6" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="BI6" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="BJ6" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="BK6" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="BL6" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="BM6" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="BN6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BO6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="BP6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BQ6">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BR6">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BS6" s="1">
-        <v>45859</v>
+        <v>45862</v>
       </c>
       <c r="BT6" s="1">
-        <v>45860</v>
+        <v>45863</v>
       </c>
       <c r="BU6" s="1">
-        <v>45861</v>
+        <v>45864</v>
       </c>
       <c r="BV6" s="6">
         <v>1</v>
@@ -6747,86 +6747,86 @@
       <c r="D13" s="7"/>
       <c r="AA13" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>250.14</v>
       </c>
       <c r="AE13" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.776554</v>
       </c>
       <c r="AG13" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8766099999999999</v>
       </c>
       <c r="AJ13" s="3">
         <f>$R5*AI5</f>
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AM13" s="3">
         <f>$R5*AL5</f>
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP13" s="3">
         <f>($AA13-AJ13-AM13)*AO5%</f>
-        <v>0</v>
+        <v>3.1232879999999996</v>
       </c>
       <c r="AS13" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11.036452000000001</v>
       </c>
       <c r="AU13" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>239.10354799999999</v>
       </c>
       <c r="BA13" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>31.08242576</v>
       </c>
       <c r="BB13" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>270.19</v>
       </c>
     </row>
     <row r="14" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D14" s="7"/>
       <c r="AA14" s="3">
         <f t="shared" si="0"/>
-        <v>250.14</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="3">
         <f t="shared" si="5"/>
-        <v>2.776554</v>
+        <v>0</v>
       </c>
       <c r="AG14" s="3">
         <f t="shared" si="5"/>
-        <v>2.8766099999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ14" s="3">
         <f>$R6*AI6</f>
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AM14" s="3">
         <f>$R6*AL6</f>
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP14" s="3">
         <f>($AA14-AJ14-AM14)*AO6%</f>
-        <v>3.1232879999999996</v>
+        <v>0</v>
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="1"/>
-        <v>11.036452000000001</v>
+        <v>0</v>
       </c>
       <c r="AU14" s="3">
         <f t="shared" si="2"/>
-        <v>239.10354799999999</v>
+        <v>0</v>
       </c>
       <c r="BA14" s="3">
         <f t="shared" si="3"/>
-        <v>31.08242576</v>
+        <v>0</v>
       </c>
       <c r="BB14" s="3">
         <f t="shared" si="4"/>
-        <v>270.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">

--- a/src/main/resources/menuItems/Sales/Transactions/480464 - Sales Return with Invoice Reference-AC.xlsx
+++ b/src/main/resources/menuItems/Sales/Transactions/480464 - Sales Return with Invoice Reference-AC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\IdeaProjects\Wings-Automation\src\main\resources\menuItems\Sales\Transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6DAC46-8B8B-48F1-A9B4-AF5F47CDD76F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E339B17E-2C18-497D-8B3B-030FBE144B68}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32760" yWindow="32760" windowWidth="32760" windowHeight="32760" tabRatio="938" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5950,7 +5950,7 @@
         <v>192</v>
       </c>
       <c r="J5" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="K5" t="s">
         <v>194</v>
@@ -5968,40 +5968,40 @@
         <v>142</v>
       </c>
       <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
         <v>1</v>
       </c>
-      <c r="Q5">
+      <c r="U5">
         <v>1</v>
       </c>
-      <c r="R5">
+      <c r="V5">
         <v>1</v>
       </c>
-      <c r="S5">
+      <c r="W5">
         <v>1</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
       </c>
       <c r="X5">
         <v>500.14</v>
       </c>
       <c r="Y5">
-        <v>500.14</v>
+        <v>0</v>
       </c>
       <c r="Z5">
         <v>250.14</v>
       </c>
       <c r="AA5">
-        <v>250.14</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="5">
         <v>0</v>
@@ -6013,13 +6013,13 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="AE5">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.1499999999999999</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="AG5">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="s">
         <v>195</v>
@@ -6028,7 +6028,7 @@
         <v>1.05</v>
       </c>
       <c r="AJ5">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="s">
         <v>195</v>
@@ -6037,7 +6037,7 @@
         <v>1.21</v>
       </c>
       <c r="AM5">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="s">
         <v>196</v>
@@ -6046,7 +6046,7 @@
         <v>1.26</v>
       </c>
       <c r="AP5">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AQ5">
         <v>0</v>
@@ -6061,31 +6061,31 @@
         <v>146</v>
       </c>
       <c r="AU5">
-        <v>239.1</v>
+        <v>0</v>
       </c>
       <c r="AV5">
         <v>12</v>
       </c>
       <c r="AW5">
-        <v>14.35</v>
+        <v>0</v>
       </c>
       <c r="AX5">
-        <v>14.35</v>
+        <v>0</v>
       </c>
       <c r="AY5">
         <v>0</v>
       </c>
       <c r="AZ5">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BA5">
-        <v>31.09</v>
+        <v>0</v>
       </c>
       <c r="BB5">
-        <v>270.19</v>
+        <v>0</v>
       </c>
       <c r="BC5">
-        <v>270.19</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="s">
         <v>197</v>
@@ -6100,46 +6100,46 @@
         <v>200</v>
       </c>
       <c r="BH5" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="BI5" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="BJ5" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="BK5" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="BL5" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="BM5" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="BN5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BO5">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="BP5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BQ5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BR5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BS5" s="1">
-        <v>45859</v>
+        <v>45862</v>
       </c>
       <c r="BT5" s="1">
-        <v>45860</v>
+        <v>45863</v>
       </c>
       <c r="BU5" s="1">
-        <v>45861</v>
+        <v>45864</v>
       </c>
       <c r="BV5" s="6">
         <v>1</v>
@@ -6180,7 +6180,7 @@
         <v>192</v>
       </c>
       <c r="J6" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="K6" t="s">
         <v>194</v>
@@ -6198,40 +6198,40 @@
         <v>142</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6">
         <v>500.14</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>500.14</v>
       </c>
       <c r="Z6">
         <v>250.14</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>250.14</v>
       </c>
       <c r="AB6" s="5">
         <v>0</v>
@@ -6243,13 +6243,13 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF6">
-        <v>1.1599999999999999</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH6" t="s">
         <v>195</v>
@@ -6258,7 +6258,7 @@
         <v>1.05</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK6" t="s">
         <v>195</v>
@@ -6267,7 +6267,7 @@
         <v>1.21</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN6" t="s">
         <v>196</v>
@@ -6276,7 +6276,7 @@
         <v>1.26</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AQ6">
         <v>0</v>
@@ -6291,31 +6291,31 @@
         <v>146</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>239.1</v>
       </c>
       <c r="AV6">
         <v>12</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>14.35</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>14.35</v>
       </c>
       <c r="AY6">
         <v>0</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>31.09</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>270.19</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>270.19</v>
       </c>
       <c r="BD6" t="s">
         <v>197</v>
@@ -6330,46 +6330,46 @@
         <v>200</v>
       </c>
       <c r="BH6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="BI6" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="BJ6" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="BK6" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="BL6" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="BM6" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="BN6">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO6">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BP6">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="BQ6">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BR6">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BS6" s="1">
-        <v>45862</v>
+        <v>45859</v>
       </c>
       <c r="BT6" s="1">
-        <v>45863</v>
+        <v>45860</v>
       </c>
       <c r="BU6" s="1">
-        <v>45864</v>
+        <v>45861</v>
       </c>
       <c r="BV6" s="6">
         <v>1</v>
@@ -6747,86 +6747,86 @@
       <c r="D13" s="7"/>
       <c r="AA13" s="3">
         <f t="shared" si="0"/>
-        <v>250.14</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="3">
         <f t="shared" si="5"/>
-        <v>2.776554</v>
+        <v>0</v>
       </c>
       <c r="AG13" s="3">
         <f t="shared" si="5"/>
-        <v>2.8766099999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ13" s="3">
         <f>$R5*AI5</f>
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AM13" s="3">
         <f>$R5*AL5</f>
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AP13" s="3">
         <f>($AA13-AJ13-AM13)*AO5%</f>
-        <v>3.1232879999999996</v>
+        <v>0</v>
       </c>
       <c r="AS13" s="3">
         <f t="shared" si="1"/>
-        <v>11.036452000000001</v>
+        <v>0</v>
       </c>
       <c r="AU13" s="3">
         <f t="shared" si="2"/>
-        <v>239.10354799999999</v>
+        <v>0</v>
       </c>
       <c r="BA13" s="3">
         <f t="shared" si="3"/>
-        <v>31.08242576</v>
+        <v>0</v>
       </c>
       <c r="BB13" s="3">
         <f t="shared" si="4"/>
-        <v>270.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D14" s="7"/>
       <c r="AA14" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>250.14</v>
       </c>
       <c r="AE14" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.776554</v>
       </c>
       <c r="AG14" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.8766099999999999</v>
       </c>
       <c r="AJ14" s="3">
         <f>$R6*AI6</f>
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AM14" s="3">
         <f>$R6*AL6</f>
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AP14" s="3">
         <f>($AA14-AJ14-AM14)*AO6%</f>
-        <v>0</v>
+        <v>3.1232879999999996</v>
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11.036452000000001</v>
       </c>
       <c r="AU14" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>239.10354799999999</v>
       </c>
       <c r="BA14" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>31.08242576</v>
       </c>
       <c r="BB14" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>270.19</v>
       </c>
     </row>
     <row r="15" spans="1:76" s="3" customFormat="1" x14ac:dyDescent="0.25">
